--- a/product-definitions/spreadsheet/sonde.xlsx
+++ b/product-definitions/spreadsheet/sonde.xlsx
@@ -216,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -242,11 +242,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -267,7 +262,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -288,33 +283,32 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1666,7 +1660,7 @@
       <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1706,7 +1700,7 @@
       <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -1714,31 +1708,31 @@
       <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="12"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="12"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12">
       <c r="B12" s="7" t="s">
@@ -1757,7 +1751,7 @@
       <c r="B15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1773,7 +1767,7 @@
       <c r="B17" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1797,35 +1791,35 @@
       <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="7" t="s">
         <v>25</v>
       </c>
@@ -1833,20 +1827,21 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26">
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="7" t="s">
         <v>12</v>
       </c>
@@ -1854,15 +1849,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="7" t="s">
         <v>15</v>
       </c>
@@ -1870,7 +1865,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="7" t="s">
         <v>16</v>
       </c>
@@ -1878,39 +1873,39 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="7" t="s">
         <v>25</v>
       </c>
@@ -1918,20 +1913,21 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38">
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="7" t="s">
         <v>12</v>
       </c>
@@ -1939,7 +1935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="7" t="s">
         <v>2</v>
       </c>
@@ -1947,7 +1943,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="7" t="s">
         <v>15</v>
       </c>
@@ -1955,68 +1951,69 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50">
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="7" t="s">
         <v>12</v>
       </c>
@@ -2024,7 +2021,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="7" t="s">
         <v>2</v>
       </c>
@@ -2032,7 +2029,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="7" t="s">
         <v>15</v>
       </c>
@@ -2040,39 +2037,39 @@
         <v>41</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="7" t="s">
         <v>25</v>
       </c>
@@ -2080,28 +2077,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62">
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="7" t="s">
         <v>12</v>
       </c>
@@ -2109,7 +2107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="B65" s="7" t="s">
         <v>2</v>
       </c>
@@ -2117,7 +2115,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="B66" s="7" t="s">
         <v>15</v>
       </c>
@@ -2125,39 +2123,39 @@
         <v>44</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="7" t="s">
         <v>25</v>
       </c>
@@ -2165,28 +2163,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="74">
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="7" t="s">
         <v>12</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="7" t="s">
         <v>2</v>
       </c>
@@ -2202,7 +2201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="7" t="s">
         <v>15</v>
       </c>
@@ -2210,7 +2209,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="7" t="s">
         <v>16</v>
       </c>
@@ -2218,31 +2217,31 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="7" t="s">
         <v>25</v>
       </c>
@@ -2250,28 +2249,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="86">
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="7" t="s">
         <v>12</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="7" t="s">
         <v>2</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="7" t="s">
         <v>15</v>
       </c>
@@ -2295,39 +2295,39 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C93" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="B94" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="7" t="s">
         <v>25</v>
       </c>
@@ -2335,28 +2335,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="98">
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="7" t="s">
         <v>12</v>
       </c>
@@ -2364,7 +2365,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="7" t="s">
         <v>2</v>
       </c>
@@ -2372,7 +2373,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="7" t="s">
         <v>15</v>
       </c>
@@ -2380,7 +2381,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="7" t="s">
         <v>16</v>
       </c>
@@ -2388,31 +2389,31 @@
         <v>54</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C106" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="7" t="s">
         <v>25</v>
       </c>
@@ -2420,28 +2421,29 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="110">
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="7" t="s">
         <v>12</v>
       </c>
@@ -2449,7 +2451,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="7" t="s">
         <v>2</v>
       </c>
@@ -2457,7 +2459,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="7" t="s">
         <v>15</v>
       </c>
@@ -2465,7 +2467,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="7" t="s">
         <v>16</v>
       </c>
@@ -2473,44 +2475,45 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="8">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C118" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="120">
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="B121" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="B122" s="7" t="s">
         <v>12</v>
       </c>
@@ -2518,21 +2521,21 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C123" s="14">
+      <c r="C123" s="13">
         <v>1.0</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C124" s="14"/>
-    </row>
-    <row r="125">
+      <c r="C124" s="13"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="7" t="s">
         <v>16</v>
       </c>
@@ -2540,42 +2543,42 @@
         <v>60</v>
       </c>
     </row>
-    <row r="126">
-      <c r="B126" s="10" t="s">
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="B126" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C126" s="15" t="s">
+      <c r="C126" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="16" t="s">
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="B127" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="C127" s="16" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="128" ht="12.0" customHeight="1">
-      <c r="B128" s="10"/>
-      <c r="C128" s="10"/>
+      <c r="B128" s="9"/>
+      <c r="C128" s="9"/>
     </row>
     <row r="129" ht="12.0" customHeight="1"/>
     <row r="130" ht="12.0" customHeight="1"/>
     <row r="131" ht="12.0" customHeight="1"/>
     <row r="132" ht="12.0" customHeight="1"/>
     <row r="133" ht="12.0" customHeight="1">
-      <c r="C133" s="14"/>
+      <c r="C133" s="13"/>
     </row>
     <row r="134" ht="12.0" customHeight="1">
-      <c r="C134" s="14"/>
+      <c r="C134" s="13"/>
     </row>
     <row r="135" ht="12.0" customHeight="1"/>
     <row r="136" ht="12.0" customHeight="1">
-      <c r="C136" s="14"/>
+      <c r="C136" s="13"/>
     </row>
     <row r="137" ht="12.0" customHeight="1">
-      <c r="C137" s="14"/>
+      <c r="C137" s="13"/>
     </row>
     <row r="138" ht="12.0" customHeight="1"/>
     <row r="139" ht="12.0" customHeight="1"/>
@@ -2583,17 +2586,17 @@
     <row r="141" ht="12.0" customHeight="1"/>
     <row r="142" ht="12.0" customHeight="1"/>
     <row r="143" ht="12.0" customHeight="1">
-      <c r="C143" s="14"/>
+      <c r="C143" s="13"/>
     </row>
     <row r="144" ht="12.0" customHeight="1">
-      <c r="C144" s="14"/>
+      <c r="C144" s="13"/>
     </row>
     <row r="145" ht="12.0" customHeight="1"/>
     <row r="146" ht="12.0" customHeight="1">
-      <c r="C146" s="14"/>
+      <c r="C146" s="13"/>
     </row>
     <row r="147" ht="12.0" customHeight="1">
-      <c r="C147" s="14"/>
+      <c r="C147" s="13"/>
     </row>
     <row r="148" ht="12.0" customHeight="1"/>
     <row r="149" ht="12.0" customHeight="1"/>
@@ -2601,17 +2604,17 @@
     <row r="151" ht="12.0" customHeight="1"/>
     <row r="152" ht="12.0" customHeight="1"/>
     <row r="153" ht="12.0" customHeight="1">
-      <c r="C153" s="14"/>
+      <c r="C153" s="13"/>
     </row>
     <row r="154" ht="12.0" customHeight="1">
-      <c r="C154" s="14"/>
+      <c r="C154" s="13"/>
     </row>
     <row r="155" ht="12.0" customHeight="1"/>
     <row r="156" ht="12.0" customHeight="1">
-      <c r="C156" s="14"/>
+      <c r="C156" s="13"/>
     </row>
     <row r="157" ht="12.0" customHeight="1">
-      <c r="C157" s="14"/>
+      <c r="C157" s="13"/>
     </row>
     <row r="158" ht="12.0" customHeight="1"/>
     <row r="159" ht="12.0" customHeight="1"/>
@@ -2619,17 +2622,17 @@
     <row r="161" ht="12.0" customHeight="1"/>
     <row r="162" ht="12.0" customHeight="1"/>
     <row r="163" ht="12.0" customHeight="1">
-      <c r="C163" s="14"/>
+      <c r="C163" s="13"/>
     </row>
     <row r="164" ht="12.0" customHeight="1">
-      <c r="C164" s="14"/>
+      <c r="C164" s="13"/>
     </row>
     <row r="165" ht="12.0" customHeight="1"/>
     <row r="166" ht="12.0" customHeight="1">
-      <c r="C166" s="14"/>
+      <c r="C166" s="13"/>
     </row>
     <row r="167" ht="12.0" customHeight="1">
-      <c r="C167" s="14"/>
+      <c r="C167" s="13"/>
     </row>
     <row r="168" ht="12.0" customHeight="1"/>
     <row r="169" ht="12.0" customHeight="1"/>
@@ -2637,14 +2640,14 @@
     <row r="171" ht="12.0" customHeight="1"/>
     <row r="172" ht="12.0" customHeight="1"/>
     <row r="173" ht="12.0" customHeight="1">
-      <c r="C173" s="14"/>
+      <c r="C173" s="13"/>
     </row>
     <row r="174" ht="12.0" customHeight="1">
-      <c r="C174" s="14"/>
+      <c r="C174" s="13"/>
     </row>
     <row r="175" ht="12.0" customHeight="1"/>
     <row r="176" ht="12.0" customHeight="1">
-      <c r="C176" s="14"/>
+      <c r="C176" s="13"/>
     </row>
     <row r="177" ht="12.0" customHeight="1"/>
     <row r="178" ht="12.0" customHeight="1"/>
